--- a/設計資料/ペアプログラミング2_チーム2_基本仕様R0.xlsx
+++ b/設計資料/ペアプログラミング2_チーム2_基本仕様R0.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s_ochi\Documents\JOB\ITC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s_ochi\Documents\GitHub\WebAPI_Pair_Programming_Team2\設計資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1791B880-F869-4E80-8861-71FFF15C3B53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5860AA4-4048-499D-84D3-69CC7E4347D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23850" yWindow="2655" windowWidth="21600" windowHeight="11295" activeTab="7" xr2:uid="{364D4863-AD58-4424-8EC0-C144B033B4FB}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{364D4863-AD58-4424-8EC0-C144B033B4FB}"/>
   </bookViews>
   <sheets>
     <sheet name="スケジュール" sheetId="1" r:id="rId1"/>
@@ -1584,14 +1584,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1650,12 +1647,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3718,7 +3709,7 @@
       <c r="D3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>52</v>
       </c>
     </row>
@@ -3728,7 +3719,7 @@
       <c r="D4" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3738,7 +3729,7 @@
       <c r="D5" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3748,7 +3739,7 @@
       <c r="D6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3758,7 +3749,7 @@
       <c r="D7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3776,7 +3767,7 @@
       <c r="D9" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="4" t="s">
         <v>58</v>
       </c>
     </row>
@@ -3788,7 +3779,7 @@
       <c r="D10" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3808,7 +3799,7 @@
       <c r="D12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3818,7 +3809,7 @@
       <c r="D13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="1" t="s">
         <v>51</v>
       </c>
     </row>
@@ -3935,7 +3926,7 @@
       <c r="B5" t="s">
         <v>306</v>
       </c>
-      <c r="N5" s="3" t="s">
+      <c r="N5" s="2" t="s">
         <v>78</v>
       </c>
     </row>
@@ -3951,7 +3942,7 @@
       <c r="K7" t="s">
         <v>75</v>
       </c>
-      <c r="N7" s="3"/>
+      <c r="N7" s="2"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B8" t="s">
@@ -3962,7 +3953,7 @@
       <c r="B9" t="s">
         <v>310</v>
       </c>
-      <c r="N9" s="3" t="s">
+      <c r="N9" s="2" t="s">
         <v>77</v>
       </c>
     </row>
@@ -3994,13 +3985,13 @@
       <c r="K14" t="s">
         <v>26</v>
       </c>
-      <c r="N14" s="3"/>
+      <c r="N14" s="2"/>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.4">
       <c r="C15" t="s">
         <v>313</v>
       </c>
-      <c r="N15" s="3"/>
+      <c r="N15" s="2"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.4">
       <c r="C16" t="s">
@@ -4009,7 +4000,7 @@
       <c r="K16" t="s">
         <v>22</v>
       </c>
-      <c r="N16" s="3" t="s">
+      <c r="N16" s="2" t="s">
         <v>76</v>
       </c>
     </row>
@@ -4017,19 +4008,19 @@
       <c r="C17" t="s">
         <v>143</v>
       </c>
-      <c r="N17" s="3"/>
+      <c r="N17" s="2"/>
     </row>
     <row r="18" spans="2:14" x14ac:dyDescent="0.4">
       <c r="K18" t="s">
         <v>23</v>
       </c>
-      <c r="N18" s="3"/>
+      <c r="N18" s="2"/>
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B19" t="s">
         <v>305</v>
       </c>
-      <c r="N19" s="3"/>
+      <c r="N19" s="2"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B20" t="s">
@@ -4038,7 +4029,7 @@
       <c r="C20" t="s">
         <v>315</v>
       </c>
-      <c r="N20" s="3" t="s">
+      <c r="N20" s="2" t="s">
         <v>78</v>
       </c>
     </row>
@@ -4049,7 +4040,7 @@
       <c r="C21" t="s">
         <v>312</v>
       </c>
-      <c r="N21" s="3"/>
+      <c r="N21" s="2"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.4">
       <c r="C22" t="s">
@@ -4322,36 +4313,36 @@
       </c>
     </row>
     <row r="3" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="6" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="4" spans="2:6" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>41</v>
       </c>
     </row>
@@ -4362,7 +4353,7 @@
       <c r="C5" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>47</v>
       </c>
       <c r="E5" s="1" t="s">
@@ -4379,7 +4370,7 @@
       <c r="C6" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>47</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -4391,13 +4382,13 @@
       <c r="B7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>46</v>
       </c>
       <c r="F7" s="1"/>
@@ -4408,34 +4399,34 @@
       </c>
     </row>
     <row r="10" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7" t="s">
+      <c r="D10" s="6"/>
+      <c r="E10" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="7" t="s">
+      <c r="F10" s="6" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="11" spans="2:6" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="5" t="s">
         <v>42</v>
       </c>
     </row>
@@ -4446,7 +4437,7 @@
       <c r="C12" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="5" t="s">
         <v>47</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -4461,7 +4452,7 @@
       <c r="C13" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>47</v>
       </c>
       <c r="E13" s="1" t="s">
@@ -4480,346 +4471,346 @@
   <dimension ref="B2:L27"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="9" style="8"/>
-    <col min="2" max="2" width="28.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.125" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9" style="8"/>
-    <col min="5" max="5" width="28.75" style="8" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="38.125" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9" style="8"/>
-    <col min="8" max="8" width="19" style="8" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="38.125" style="8" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9" style="8"/>
-    <col min="11" max="11" width="19" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="38.125" style="8" bestFit="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="8"/>
+    <col min="1" max="1" width="9" style="7"/>
+    <col min="2" max="2" width="28.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="7"/>
+    <col min="5" max="5" width="28.75" style="7" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="38.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="7"/>
+    <col min="8" max="8" width="19" style="7" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="38.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9" style="7"/>
+    <col min="11" max="11" width="19" style="7" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="38.125" style="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="K2" s="9" t="s">
+      <c r="K2" s="8" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="K3" s="10" t="s">
+      <c r="K3" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="L3" s="10" t="s">
+      <c r="L3" s="9" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="4" spans="2:12" ht="19.5" thickTop="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="L4" s="10" t="s">
         <v>140</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="H5" s="12" t="s">
+      <c r="H5" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="K5" s="12" t="s">
+      <c r="K5" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="L5" s="12" t="s">
+      <c r="L5" s="11" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="6" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="H6" s="12" t="s">
+      <c r="H6" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="K6" s="12" t="s">
+      <c r="K6" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="L6" s="12" t="s">
+      <c r="L6" s="11" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="E7" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="F7" s="12" t="s">
+      <c r="F7" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="H7" s="12" t="s">
+      <c r="H7" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="I7" s="12" t="s">
+      <c r="I7" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="K7" s="12" t="s">
+      <c r="K7" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="L7" s="12" t="s">
+      <c r="L7" s="11" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="8" spans="2:12" ht="75" x14ac:dyDescent="0.4">
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="12" t="s">
         <v>137</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="H8" s="12" t="s">
+      <c r="H8" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="I8" s="13" t="s">
+      <c r="I8" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="K8" s="12" t="s">
+      <c r="K8" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="L8" s="13" t="s">
+      <c r="L8" s="12" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B10" s="8" t="s">
+      <c r="B10" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="E10" s="8" t="s">
+      <c r="E10" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="H10" s="14" t="s">
+      <c r="H10" s="13" t="s">
         <v>116</v>
       </c>
-      <c r="K10" s="14" t="s">
+      <c r="K10" s="13" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B11" s="8" t="s">
+      <c r="B11" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="E11" s="8" t="s">
+      <c r="E11" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="H11" s="14" t="s">
+      <c r="H11" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="K11" s="14" t="s">
+      <c r="K11" s="13" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="H12" s="14" t="s">
+      <c r="H12" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="K12" s="14" t="s">
+      <c r="K12" s="13" t="s">
         <v>126</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="E13" s="8" t="s">
+      <c r="E13" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="H13" s="14" t="s">
+      <c r="H13" s="13" t="s">
         <v>125</v>
       </c>
-      <c r="K13" s="14" t="s">
+      <c r="K13" s="13" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="E14" s="8" t="s">
+      <c r="E14" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="H14" s="14" t="s">
+      <c r="H14" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="K14" s="14" t="s">
+      <c r="K14" s="13" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="H15" s="14" t="s">
+      <c r="H15" s="13" t="s">
         <v>128</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="H16" s="14" t="s">
+      <c r="H16" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="K16" s="14"/>
+      <c r="K16" s="13"/>
     </row>
     <row r="17" spans="5:11" x14ac:dyDescent="0.4">
-      <c r="E17" s="15" t="s">
+      <c r="E17" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="H17" s="14" t="s">
+      <c r="H17" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="K17" s="14"/>
+      <c r="K17" s="13"/>
     </row>
     <row r="18" spans="5:11" x14ac:dyDescent="0.4">
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="14" t="s">
         <v>146</v>
       </c>
-      <c r="H18" s="14" t="s">
+      <c r="H18" s="13" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="19" spans="5:11" x14ac:dyDescent="0.4">
-      <c r="E19" s="15" t="s">
+      <c r="E19" s="14" t="s">
         <v>147</v>
       </c>
-      <c r="H19" s="14" t="s">
+      <c r="H19" s="13" t="s">
         <v>129</v>
       </c>
-      <c r="K19" s="14"/>
+      <c r="K19" s="13"/>
     </row>
     <row r="20" spans="5:11" x14ac:dyDescent="0.4">
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="H20" s="14" t="s">
+      <c r="H20" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="K20" s="14"/>
+      <c r="K20" s="13"/>
     </row>
     <row r="21" spans="5:11" x14ac:dyDescent="0.4">
-      <c r="H21" s="14" t="s">
+      <c r="H21" s="13" t="s">
         <v>149</v>
       </c>
-      <c r="K21" s="14"/>
+      <c r="K21" s="13"/>
     </row>
     <row r="22" spans="5:11" x14ac:dyDescent="0.4">
-      <c r="H22" s="14" t="s">
+      <c r="H22" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="K22" s="14"/>
+      <c r="K22" s="13"/>
     </row>
     <row r="23" spans="5:11" x14ac:dyDescent="0.4">
-      <c r="H23" s="14" t="s">
+      <c r="H23" s="13" t="s">
         <v>152</v>
       </c>
-      <c r="K23" s="14"/>
+      <c r="K23" s="13"/>
     </row>
     <row r="24" spans="5:11" x14ac:dyDescent="0.4">
-      <c r="H24" s="14" t="s">
+      <c r="H24" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="K24" s="14"/>
+      <c r="K24" s="13"/>
     </row>
     <row r="25" spans="5:11" x14ac:dyDescent="0.4">
-      <c r="H25" s="14" t="s">
+      <c r="H25" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="K25" s="14"/>
+      <c r="K25" s="13"/>
     </row>
     <row r="26" spans="5:11" x14ac:dyDescent="0.4">
-      <c r="H26" s="14"/>
-      <c r="K26" s="14"/>
+      <c r="H26" s="13"/>
+      <c r="K26" s="13"/>
     </row>
     <row r="27" spans="5:11" x14ac:dyDescent="0.4">
-      <c r="K27" s="14"/>
+      <c r="K27" s="13"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -4833,7 +4824,7 @@
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="17.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="26.25" style="8" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.25" style="7" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="43.125" customWidth="1"/>
     <col min="4" max="4" width="12.25" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.25" bestFit="1" customWidth="1"/>
@@ -4841,13 +4832,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>203</v>
       </c>
       <c r="C2" t="s">
         <v>177</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="17" t="s">
         <v>204</v>
       </c>
       <c r="F2" t="s">
@@ -4855,92 +4846,92 @@
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="17" t="s">
         <v>176</v>
       </c>
       <c r="C3" t="s">
         <v>175</v>
       </c>
-      <c r="E3" s="8"/>
+      <c r="E3" s="7"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="17" t="s">
         <v>178</v>
       </c>
-      <c r="E5" s="18" t="s">
+      <c r="E5" s="17" t="s">
         <v>178</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B6" s="17" t="s">
+      <c r="B6" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C6" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="F6" s="17" t="s">
+      <c r="F6" s="16" t="s">
         <v>205</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="19" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="19" t="s">
         <v>93</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="19" t="s">
         <v>207</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="E9" s="19" t="s">
         <v>92</v>
       </c>
-      <c r="F9" s="20" t="s">
+      <c r="F9" s="19" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B10" s="19"/>
-      <c r="C10" s="4"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="3"/>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="17" t="s">
         <v>119</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="17" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B12" s="8" t="s">
+      <c r="B12" s="7" t="s">
         <v>179</v>
       </c>
       <c r="E12" t="s">
@@ -4948,7 +4939,7 @@
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B13" s="8" t="s">
+      <c r="B13" s="7" t="s">
         <v>180</v>
       </c>
       <c r="E13" t="s">
@@ -4956,7 +4947,7 @@
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B14" s="8" t="s">
+      <c r="B14" s="7" t="s">
         <v>181</v>
       </c>
       <c r="E14" t="s">
@@ -4964,7 +4955,7 @@
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B15" s="8" t="s">
+      <c r="B15" s="7" t="s">
         <v>202</v>
       </c>
       <c r="E15" t="s">
@@ -4972,7 +4963,7 @@
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="7" t="s">
         <v>182</v>
       </c>
       <c r="E16" t="s">
@@ -4980,17 +4971,17 @@
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="7" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="17" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="17" t="s">
         <v>199</v>
       </c>
       <c r="E19" t="s">
@@ -4998,7 +4989,7 @@
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="7" t="s">
         <v>184</v>
       </c>
       <c r="E20" t="s">
@@ -5006,7 +4997,7 @@
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="7" t="s">
         <v>180</v>
       </c>
       <c r="E21" t="s">
@@ -5014,7 +5005,7 @@
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="7" t="s">
         <v>185</v>
       </c>
       <c r="E22" t="s">
@@ -5022,20 +5013,20 @@
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B23" s="8" t="s">
+      <c r="B23" s="7" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B24" s="8" t="s">
+      <c r="B24" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="E24" s="17" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B25" s="8" t="s">
+      <c r="B25" s="7" t="s">
         <v>188</v>
       </c>
       <c r="E25" t="s">
@@ -5048,7 +5039,7 @@
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="17" t="s">
         <v>200</v>
       </c>
       <c r="E27" t="s">
@@ -5056,7 +5047,7 @@
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B28" s="8" t="s">
+      <c r="B28" s="7" t="s">
         <v>189</v>
       </c>
       <c r="E28" t="s">
@@ -5064,7 +5055,7 @@
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B29" s="8" t="s">
+      <c r="B29" s="7" t="s">
         <v>190</v>
       </c>
       <c r="E29" t="s">
@@ -5072,7 +5063,7 @@
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B30" s="8" t="s">
+      <c r="B30" s="7" t="s">
         <v>191</v>
       </c>
       <c r="E30" t="s">
@@ -5080,42 +5071,42 @@
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.4">
-      <c r="B31" s="8" t="s">
+      <c r="B31" s="7" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B33" s="18" t="s">
+      <c r="B33" s="17" t="s">
         <v>201</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="7" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B35" s="8" t="s">
+      <c r="B35" s="7" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B36" s="8" t="s">
+      <c r="B36" s="7" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B37" s="8" t="s">
+      <c r="B37" s="7" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B38" s="8" t="s">
+      <c r="B38" s="7" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B39" s="8" t="s">
+      <c r="B39" s="7" t="s">
         <v>198</v>
       </c>
     </row>
@@ -5519,593 +5510,593 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="17" t="s">
         <v>225</v>
       </c>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="17" t="s">
         <v>239</v>
       </c>
     </row>
     <row r="4" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="D4" s="15" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="4">
         <v>201</v>
       </c>
     </row>
     <row r="6" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6" s="4">
         <v>201</v>
       </c>
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7" s="4">
         <v>201</v>
       </c>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D8" s="4">
         <v>201</v>
       </c>
     </row>
     <row r="9" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="20" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="10" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="C10" s="16" t="s">
+      <c r="C10" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="15" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="11" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="D11" s="5">
+      <c r="D11" s="4">
         <v>400</v>
       </c>
     </row>
     <row r="12" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="D12" s="5">
+      <c r="D12" s="4">
         <v>400</v>
       </c>
     </row>
     <row r="13" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D13" s="5">
+      <c r="D13" s="4">
         <v>400</v>
       </c>
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="D14" s="5">
+      <c r="D14" s="4">
         <v>400</v>
       </c>
     </row>
     <row r="15" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="4">
         <v>400</v>
       </c>
     </row>
     <row r="18" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="17" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="19" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="17" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="20" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="15" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="D21" s="5">
+      <c r="D21" s="4">
         <v>200</v>
       </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="4" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="23" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B23" s="21" t="s">
+      <c r="B23" s="20" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="15" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="D25" s="5">
+      <c r="D25" s="4">
         <v>400</v>
       </c>
     </row>
     <row r="26" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D26" s="5">
+      <c r="D26" s="4">
         <v>400</v>
       </c>
     </row>
     <row r="27" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="D27" s="5">
+      <c r="D27" s="4">
         <v>400</v>
       </c>
     </row>
     <row r="28" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="D28" s="5">
+      <c r="D28" s="4">
         <v>400</v>
       </c>
     </row>
     <row r="30" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B30" s="18" t="s">
+      <c r="B30" s="17" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B31" s="18" t="s">
+      <c r="B31" s="17" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="32" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B32" s="16" t="s">
+      <c r="B32" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="D32" s="16" t="s">
+      <c r="D32" s="15" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="4" t="s">
         <v>260</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="D33" s="5">
+      <c r="D33" s="4">
         <v>200</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="D34" s="5">
+      <c r="D34" s="4">
         <v>200</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="4" t="s">
         <v>264</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="D35" s="5" t="s">
+      <c r="D35" s="4" t="s">
         <v>292</v>
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B36" s="21" t="s">
+      <c r="B36" s="20" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B37" s="16" t="s">
+      <c r="B37" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="C37" s="16" t="s">
+      <c r="C37" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="D37" s="16" t="s">
+      <c r="D37" s="15" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="4" t="s">
         <v>266</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="D38" s="5">
+      <c r="D38" s="4">
         <v>500</v>
       </c>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B41" s="18" t="s">
+      <c r="B41" s="17" t="s">
         <v>268</v>
       </c>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B42" s="18" t="s">
+      <c r="B42" s="17" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B43" s="16" t="s">
+      <c r="B43" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="C43" s="16" t="s">
+      <c r="C43" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="D43" s="16" t="s">
+      <c r="D43" s="15" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="4" t="s">
         <v>302</v>
       </c>
-      <c r="D44" s="5">
+      <c r="D44" s="4">
         <v>201</v>
       </c>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="D45" s="5">
+      <c r="D45" s="4">
         <v>201</v>
       </c>
     </row>
     <row r="46" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B46" s="21" t="s">
+      <c r="B46" s="20" t="s">
         <v>237</v>
       </c>
     </row>
     <row r="47" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B47" s="16" t="s">
+      <c r="B47" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="C47" s="16" t="s">
+      <c r="C47" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="D47" s="16" t="s">
+      <c r="D47" s="15" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C48" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="D48" s="5">
+      <c r="D48" s="4">
         <v>400</v>
       </c>
     </row>
     <row r="49" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B49" s="5" t="s">
+      <c r="B49" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C49" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="D49" s="5">
+      <c r="D49" s="4">
         <v>400</v>
       </c>
     </row>
     <row r="50" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="C50" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="D50" s="5">
+      <c r="D50" s="4">
         <v>400</v>
       </c>
     </row>
     <row r="53" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B53" s="18" t="s">
+      <c r="B53" s="17" t="s">
         <v>277</v>
       </c>
     </row>
     <row r="54" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B54" s="18" t="s">
+      <c r="B54" s="17" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="55" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B55" s="16" t="s">
+      <c r="B55" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="C55" s="16" t="s">
+      <c r="C55" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="D55" s="16" t="s">
+      <c r="D55" s="15" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="56" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B56" s="5" t="s">
+      <c r="B56" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="C56" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D56" s="5" t="s">
+      <c r="D56" s="4" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="57" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B57" s="5" t="s">
+      <c r="B57" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="C57" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="D57" s="5" t="s">
+      <c r="D57" s="4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="58" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B58" s="5" t="s">
+      <c r="B58" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="C58" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="D58" s="5" t="s">
+      <c r="D58" s="4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B60" s="23" t="s">
+      <c r="B60" s="17" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B61" s="16" t="s">
+      <c r="B61" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="C61" s="16" t="s">
+      <c r="C61" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="D61" s="16" t="s">
+      <c r="D61" s="15" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="62" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B62" s="5" t="s">
+      <c r="B62" s="4" t="s">
         <v>282</v>
       </c>
-      <c r="C62" s="5" t="s">
+      <c r="C62" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="D62" s="5" t="s">
+      <c r="D62" s="4" t="s">
         <v>283</v>
       </c>
     </row>
     <row r="63" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B63" s="5" t="s">
+      <c r="B63" s="4" t="s">
         <v>284</v>
       </c>
-      <c r="C63" s="5" t="s">
+      <c r="C63" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="D63" s="5" t="s">
+      <c r="D63" s="4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="64" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B64" s="5" t="s">
+      <c r="B64" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="C64" s="5" t="s">
+      <c r="C64" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="D64" s="5" t="s">
+      <c r="D64" s="4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="65" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B65" s="22"/>
-      <c r="C65" s="22"/>
-      <c r="D65" s="22"/>
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+      <c r="D65" s="3"/>
     </row>
     <row r="66" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B66" s="18" t="s">
+      <c r="B66" s="17" t="s">
         <v>295</v>
       </c>
     </row>
     <row r="67" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B67" s="16" t="s">
+      <c r="B67" s="15" t="s">
         <v>226</v>
       </c>
-      <c r="C67" s="16" t="s">
+      <c r="C67" s="15" t="s">
         <v>227</v>
       </c>
-      <c r="D67" s="16" t="s">
+      <c r="D67" s="15" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="68" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B68" s="5" t="s">
+      <c r="B68" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="C68" s="5" t="s">
+      <c r="C68" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="D68" s="5" t="s">
+      <c r="D68" s="4" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="69" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B69" s="5" t="s">
+      <c r="B69" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="C69" s="5" t="s">
+      <c r="C69" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D69" s="5" t="s">
+      <c r="D69" s="4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="70" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B70" s="5" t="s">
+      <c r="B70" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="C70" s="5" t="s">
+      <c r="C70" s="4" t="s">
         <v>298</v>
       </c>
-      <c r="D70" s="5" t="s">
+      <c r="D70" s="4" t="s">
         <v>296</v>
       </c>
     </row>
     <row r="71" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B71" s="5" t="s">
+      <c r="B71" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="C71" s="5" t="s">
+      <c r="C71" s="4" t="s">
         <v>300</v>
       </c>
-      <c r="D71" s="5" t="s">
+      <c r="D71" s="4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="72" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B72" s="5" t="s">
+      <c r="B72" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="C72" s="5" t="s">
+      <c r="C72" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="D72" s="5" t="s">
+      <c r="D72" s="4" t="s">
         <v>83</v>
       </c>
     </row>

--- a/設計資料/ペアプログラミング2_チーム2_基本仕様R0.xlsx
+++ b/設計資料/ペアプログラミング2_チーム2_基本仕様R0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s_ochi\Documents\GitHub\WebAPI_Pair_Programming_Team2\設計資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5860AA4-4048-499D-84D3-69CC7E4347D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83F840DF-6B9A-4F16-8E16-26B0A811F886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{364D4863-AD58-4424-8EC0-C144B033B4FB}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{364D4863-AD58-4424-8EC0-C144B033B4FB}"/>
   </bookViews>
   <sheets>
     <sheet name="スケジュール" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="347">
   <si>
     <t>作るもの決定</t>
   </si>
@@ -563,9 +563,6 @@
   </si>
   <si>
     <t>},</t>
-  </si>
-  <si>
-    <t>}</t>
   </si>
   <si>
     <t xml:space="preserve">Requestユーザー登録JSON例 </t>
@@ -696,21 +693,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>201 OK 登録成功
-400 NG 入力不正
-500 Internal Server Error サーバーエラー</t>
-    <rPh sb="7" eb="9">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>フセイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Chats</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -743,12 +725,6 @@
     <t>チャット送信</t>
   </si>
   <si>
-    <t xml:space="preserve">  "userId": 1,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  "userName": "Name"</t>
-  </si>
-  <si>
     <t xml:space="preserve">  "userName": "Name",</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -766,17 +742,6 @@
   </si>
   <si>
     <t xml:space="preserve">    "createdAt": "2026-06-09T10:00:00"</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Responseログイン成功JSON例 </t>
-    <rPh sb="12" eb="14">
-      <t>セイコウ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>ログイン成功JSON</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1454,6 +1419,69 @@
   </si>
   <si>
     <t>新規ユーザーを登録する。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>201 OK 登録成功
+400 NG 入力不正
+409 ユーザー名重複
+500 Internal Server Error サーバーエラー</t>
+    <rPh sb="7" eb="9">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>フセイ</t>
+    </rPh>
+    <rPh sb="32" eb="33">
+      <t>メイ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
+      <t>チョウフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー名未入力</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー名重複</t>
+    <rPh sb="5" eb="7">
+      <t>チョウフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>U-16</t>
+  </si>
+  <si>
+    <t>ユーザー名重複</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>F-14</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>重複しているユーザー名</t>
+    <rPh sb="0" eb="2">
+      <t>チョウフク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>期待結果</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>結果</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エビデンス</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1584,7 +1612,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1647,6 +1675,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3900,7 +3931,7 @@
   <sheetData>
     <row r="2" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="K2" t="s">
         <v>55</v>
@@ -3911,20 +3942,20 @@
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="K3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B4" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B5" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>78</v>
@@ -3932,12 +3963,12 @@
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B6" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B7" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="K7" t="s">
         <v>75</v>
@@ -3946,12 +3977,12 @@
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B8" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B9" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>77</v>
@@ -3964,23 +3995,23 @@
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B12" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B13" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C13" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B14" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C14" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="K14" t="s">
         <v>26</v>
@@ -3989,13 +4020,13 @@
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.4">
       <c r="C15" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="N15" s="2"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.4">
       <c r="C16" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="K16" t="s">
         <v>22</v>
@@ -4006,7 +4037,7 @@
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.4">
       <c r="C17" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="N17" s="2"/>
     </row>
@@ -4018,16 +4049,16 @@
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B19" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="N19" s="2"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B20" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C20" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>78</v>
@@ -4035,127 +4066,127 @@
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B21" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C21" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="N21" s="2"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.4">
       <c r="C22" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.4">
       <c r="C23" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.4">
       <c r="C24" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B26" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B27" t="s">
+        <v>305</v>
+      </c>
+      <c r="C27" t="s">
         <v>311</v>
-      </c>
-      <c r="C27" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B28" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C28" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.4">
       <c r="C29" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.4">
       <c r="C30" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.4">
       <c r="C31" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B33" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B34" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C34" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B35" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C35" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C36" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C37" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C38" t="s">
-        <v>287</v>
+        <v>281</v>
       </c>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B40" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B41" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="C41" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B42" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C42" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="D42" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C43" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
       <c r="D43" t="s">
         <v>70</v>
@@ -4163,48 +4194,48 @@
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C44" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="D44" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C45" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="D45" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B48" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B49" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B50" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B51" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B52" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B53" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.4">
@@ -4212,12 +4243,12 @@
         <v>70</v>
       </c>
       <c r="C55" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C56" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.4">
@@ -4225,17 +4256,17 @@
         <v>72</v>
       </c>
       <c r="C58" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C59" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B61" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.4">
@@ -4243,22 +4274,22 @@
         <v>56</v>
       </c>
       <c r="C62" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C63" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C64" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C65" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.4">
@@ -4266,17 +4297,17 @@
         <v>54</v>
       </c>
       <c r="C67" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C68" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C69" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>
@@ -4309,7 +4340,7 @@
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -4488,16 +4519,16 @@
   <sheetData>
     <row r="2" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B2" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H2" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="K2" s="8" t="s">
         <v>139</v>
-      </c>
-      <c r="K2" s="8" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -4531,25 +4562,25 @@
         <v>96</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E4" s="10" t="s">
         <v>96</v>
       </c>
       <c r="F4" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H4" s="10" t="s">
         <v>96</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="K4" s="10" t="s">
         <v>96</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.4">
@@ -4583,25 +4614,25 @@
         <v>98</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E6" s="11" t="s">
         <v>98</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H6" s="11" t="s">
         <v>98</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="L6" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="2:12" x14ac:dyDescent="0.4">
@@ -4609,25 +4640,25 @@
         <v>99</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>154</v>
+        <v>111</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="I7" s="11" t="s">
         <v>102</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="L7" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="8" spans="2:12" ht="75" x14ac:dyDescent="0.4">
@@ -4635,13 +4666,13 @@
         <v>100</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>137</v>
+        <v>337</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>100</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="H8" s="11" t="s">
         <v>100</v>
@@ -4650,24 +4681,24 @@
         <v>101</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B10" s="7" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.4">
@@ -4681,35 +4712,35 @@
         <v>103</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B12" s="7" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>104</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B13" s="7" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.4">
@@ -4720,82 +4751,71 @@
         <v>107</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.4">
       <c r="H15" s="13" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.4">
+      <c r="H16" s="13" t="s">
+        <v>148</v>
+      </c>
+      <c r="K16" s="13"/>
+    </row>
+    <row r="17" spans="5:11" x14ac:dyDescent="0.4">
+      <c r="E17" s="14"/>
+      <c r="H17" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="K17" s="13"/>
+    </row>
+    <row r="18" spans="5:11" x14ac:dyDescent="0.4">
+      <c r="E18" s="14"/>
+      <c r="H18" s="13" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="19" spans="5:11" x14ac:dyDescent="0.4">
+      <c r="E19" s="14"/>
+      <c r="H19" s="13" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.4">
-      <c r="E16" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="K16" s="13"/>
-    </row>
-    <row r="17" spans="5:11" x14ac:dyDescent="0.4">
-      <c r="E17" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="K17" s="13"/>
-    </row>
-    <row r="18" spans="5:11" x14ac:dyDescent="0.4">
-      <c r="E18" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="H18" s="13" t="s">
+      <c r="K19" s="13"/>
+    </row>
+    <row r="20" spans="5:11" x14ac:dyDescent="0.4">
+      <c r="E20" s="14"/>
+      <c r="H20" s="13" t="s">
         <v>131</v>
-      </c>
-    </row>
-    <row r="19" spans="5:11" x14ac:dyDescent="0.4">
-      <c r="E19" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="H19" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="K19" s="13"/>
-    </row>
-    <row r="20" spans="5:11" x14ac:dyDescent="0.4">
-      <c r="E20" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="H20" s="13" t="s">
-        <v>132</v>
       </c>
       <c r="K20" s="13"/>
     </row>
     <row r="21" spans="5:11" x14ac:dyDescent="0.4">
       <c r="H21" s="13" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="K21" s="13"/>
     </row>
     <row r="22" spans="5:11" x14ac:dyDescent="0.4">
       <c r="H22" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="K22" s="13"/>
     </row>
     <row r="23" spans="5:11" x14ac:dyDescent="0.4">
       <c r="H23" s="13" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="K23" s="13"/>
     </row>
     <row r="24" spans="5:11" x14ac:dyDescent="0.4">
       <c r="H24" s="13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="K24" s="13"/>
     </row>
@@ -4833,33 +4853,33 @@
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B2" s="17" t="s">
+        <v>197</v>
+      </c>
+      <c r="C2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>198</v>
+      </c>
+      <c r="F2" t="s">
         <v>203</v>
-      </c>
-      <c r="C2" t="s">
-        <v>177</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>204</v>
-      </c>
-      <c r="F2" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B3" s="17" t="s">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C3" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="E3" s="7"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B5" s="17" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>178</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.4">
@@ -4867,13 +4887,13 @@
         <v>90</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="E6" s="16" t="s">
         <v>90</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.4">
@@ -4881,13 +4901,13 @@
         <v>91</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>174</v>
+        <v>168</v>
       </c>
       <c r="E7" s="19" t="s">
         <v>91</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.4">
@@ -4895,13 +4915,13 @@
         <v>93</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="E8" s="19" t="s">
         <v>93</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.4">
@@ -4909,13 +4929,13 @@
         <v>92</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="E9" s="19" t="s">
         <v>92</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.4">
@@ -4924,7 +4944,7 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B11" s="17" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E11" s="17" t="s">
         <v>70</v>
@@ -4932,94 +4952,94 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B12" s="7" t="s">
-        <v>179</v>
+        <v>173</v>
       </c>
       <c r="E12" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B13" s="7" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="E13" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B14" s="7" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="E14" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B15" s="7" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="E15" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B16" s="7" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="E16" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B17" s="7" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.4">
       <c r="E18" s="17" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B19" s="17" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="E19" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B20" s="7" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="E20" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B21" s="7" t="s">
-        <v>180</v>
+        <v>174</v>
       </c>
       <c r="E21" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B22" s="7" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="E22" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B23" s="7" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B24" s="7" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="E24" s="17" t="s">
         <v>72</v>
@@ -5027,87 +5047,87 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B25" s="7" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="E25" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.4">
       <c r="E26" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B27" s="17" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="E27" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B28" s="7" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="E28" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B29" s="7" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="E29" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B30" s="7" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="E30" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B31" s="7" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B33" s="17" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B34" s="7" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B35" s="7" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B36" s="7" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B37" s="7" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B38" s="7" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B39" s="7" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -5118,7 +5138,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4C105CC-4B9D-4D3B-B50E-A6A3BC7743E8}">
-  <dimension ref="B2:D44"/>
+  <dimension ref="B2:D46"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="18.5" bestFit="1" customWidth="1"/>
@@ -5169,10 +5189,10 @@
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B7" s="1" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="D7" s="1">
         <v>201</v>
@@ -5190,7 +5210,7 @@
     <row r="9" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="D9" s="1">
         <v>400</v>
@@ -5208,7 +5228,7 @@
     <row r="11" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B11" s="1"/>
       <c r="C11" s="1" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="D11" s="1">
         <v>400</v>
@@ -5230,7 +5250,7 @@
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B14" s="1" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>66</v>
@@ -5242,7 +5262,7 @@
     <row r="15" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B15" s="1"/>
       <c r="C15" s="1" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="D15" s="1">
         <v>400</v>
@@ -5251,7 +5271,7 @@
     <row r="16" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
-        <v>156</v>
+        <v>338</v>
       </c>
       <c r="D16" s="1">
         <v>400</v>
@@ -5260,7 +5280,7 @@
     <row r="17" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B17" s="1"/>
       <c r="C17" s="1" t="s">
-        <v>161</v>
+        <v>155</v>
       </c>
       <c r="D17" s="1">
         <v>400</v>
@@ -5278,7 +5298,7 @@
     <row r="19" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B19" s="1"/>
       <c r="C19" s="1" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="D19" s="1">
         <v>400</v>
@@ -5287,50 +5307,50 @@
     <row r="20" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
-        <v>64</v>
+        <v>339</v>
       </c>
       <c r="D20" s="1">
-        <v>500</v>
+        <v>409</v>
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
+      <c r="C21" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="D21" s="1">
+        <v>500</v>
+      </c>
     </row>
     <row r="22" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B23" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C23" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D22" s="1">
+      <c r="D23" s="1">
         <v>200</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B23" s="1"/>
-      <c r="C23" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="D23" s="1">
-        <v>401</v>
       </c>
     </row>
     <row r="24" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B24" s="1"/>
       <c r="C24" s="1" t="s">
-        <v>62</v>
+        <v>157</v>
       </c>
       <c r="D24" s="1">
-        <v>400</v>
+        <v>401</v>
       </c>
     </row>
     <row r="25" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B25" s="1"/>
       <c r="C25" s="1" t="s">
-        <v>156</v>
+        <v>62</v>
       </c>
       <c r="D25" s="1">
         <v>400</v>
@@ -5339,7 +5359,7 @@
     <row r="26" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B26" s="1"/>
       <c r="C26" s="1" t="s">
-        <v>74</v>
+        <v>150</v>
       </c>
       <c r="D26" s="1">
         <v>400</v>
@@ -5348,43 +5368,43 @@
     <row r="27" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B27" s="1"/>
       <c r="C27" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D27" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B28" s="1"/>
+      <c r="C28" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="D27" s="1">
+      <c r="D28" s="1">
         <v>500</v>
       </c>
     </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B29" t="s">
+    <row r="30" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B30" t="s">
         <v>69</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B30" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="31" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B31" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B32" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B32" s="1"/>
       <c r="C32" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>84</v>
@@ -5393,7 +5413,7 @@
     <row r="33" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B33" s="1"/>
       <c r="C33" s="1" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>84</v>
@@ -5402,7 +5422,7 @@
     <row r="34" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B34" s="1"/>
       <c r="C34" s="1" t="s">
-        <v>74</v>
+        <v>150</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>84</v>
@@ -5410,24 +5430,24 @@
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
+      <c r="C35" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B36" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>84</v>
-      </c>
+      <c r="B36" s="1"/>
+      <c r="C36" s="1"/>
+      <c r="D36" s="1"/>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B37" s="1"/>
+      <c r="B37" s="1" t="s">
+        <v>142</v>
+      </c>
       <c r="C37" s="1" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>84</v>
@@ -5436,7 +5456,7 @@
     <row r="38" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B38" s="1"/>
       <c r="C38" s="1" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>84</v>
@@ -5445,7 +5465,7 @@
     <row r="39" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B39" s="1"/>
       <c r="C39" s="1" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>84</v>
@@ -5454,7 +5474,7 @@
     <row r="40" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B40" s="1"/>
       <c r="C40" s="1" t="s">
-        <v>162</v>
+        <v>339</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>84</v>
@@ -5462,14 +5482,17 @@
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B41" s="1"/>
-      <c r="D41" s="1"/>
+      <c r="C41" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B42" s="1" t="s">
-        <v>73</v>
-      </c>
+      <c r="B42" s="1"/>
       <c r="C42" s="1" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>84</v>
@@ -5477,19 +5500,34 @@
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B43" s="1"/>
-      <c r="C43" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" s="1"/>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B44" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D44" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B44" s="1"/>
-      <c r="C44" s="1" t="s">
+    <row r="45" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B45" s="1"/>
+      <c r="C45" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="B46" s="1"/>
+      <c r="C46" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D46" s="1" t="s">
         <v>84</v>
       </c>
     </row>
@@ -5501,120 +5539,145 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74E5BA1B-ABE7-423B-BFCE-8BAA973AD635}">
-  <dimension ref="B2:D72"/>
+  <dimension ref="B2:F73"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="8.875" customWidth="1"/>
     <col min="3" max="3" width="35.875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="96" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B2" s="17" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.4">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B3" s="17" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.4">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B4" s="15" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.4">
+        <v>344</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>230</v>
+        <v>224</v>
       </c>
       <c r="D5" s="4">
         <v>201</v>
       </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B6" s="4" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="D6" s="4">
         <v>201</v>
       </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B7" s="4" t="s">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D7" s="4">
         <v>201</v>
       </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B8" s="4" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>236</v>
+        <v>230</v>
       </c>
       <c r="D8" s="4">
         <v>201</v>
       </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B9" s="20" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.4">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B10" s="15" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.4">
+        <v>222</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="F10" s="21" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B11" s="4" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D11" s="4">
         <v>400</v>
       </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B12" s="4" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="D12" s="4">
         <v>400</v>
       </c>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B13" s="4" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>74</v>
@@ -5622,102 +5685,139 @@
       <c r="D13" s="4">
         <v>400</v>
       </c>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B14" s="4" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="D14" s="4">
         <v>400</v>
       </c>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B15" s="4" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="D15" s="4">
         <v>400</v>
       </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B16" s="4" t="s">
+        <v>340</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="D16" s="4">
+        <v>409</v>
+      </c>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B18" s="17" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.4">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B19" s="17" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.4">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B20" s="15" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.4">
+        <v>222</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B21" s="4" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D21" s="4">
         <v>200</v>
       </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B22" s="4" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.4">
+        <v>285</v>
+      </c>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B23" s="20" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.4">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B24" s="15" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.4">
+        <v>222</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B25" s="4" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D25" s="4">
         <v>400</v>
       </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B26" s="4" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>74</v>
@@ -5725,172 +5825,214 @@
       <c r="D26" s="4">
         <v>400</v>
       </c>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B27" s="4" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="D27" s="4">
         <v>400</v>
       </c>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B28" s="4" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="D28" s="4">
         <v>400</v>
       </c>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B30" s="17" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.4">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B31" s="17" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.4">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B32" s="15" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C32" s="15" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D32" s="15" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.4">
+        <v>222</v>
+      </c>
+      <c r="E32" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="F32" s="21" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B33" s="4" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="D33" s="4">
         <v>200</v>
       </c>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B34" s="4" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="D34" s="4">
         <v>200</v>
       </c>
-    </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B35" s="4" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.4">
+        <v>286</v>
+      </c>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+    </row>
+    <row r="36" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B36" s="20" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.4">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="37" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B37" s="15" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.4">
+        <v>222</v>
+      </c>
+      <c r="E37" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="F37" s="21" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B38" s="4" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D38" s="4">
         <v>500</v>
       </c>
-    </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="E38" s="1"/>
+      <c r="F38" s="1"/>
+    </row>
+    <row r="41" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B41" s="17" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.4">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="42" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B42" s="17" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.4">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="43" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B43" s="15" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.4">
+        <v>222</v>
+      </c>
+      <c r="E43" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="F43" s="21" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="44" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B44" s="4" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="D44" s="4">
         <v>201</v>
       </c>
-    </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="E44" s="1"/>
+      <c r="F44" s="1"/>
+    </row>
+    <row r="45" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B45" s="4" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="D45" s="4">
         <v>201</v>
       </c>
-    </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+    </row>
+    <row r="46" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B46" s="20" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.4">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="47" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B47" s="15" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.4">
+        <v>222</v>
+      </c>
+      <c r="E47" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="F47" s="21" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="48" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B48" s="4" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>63</v>
@@ -5898,75 +6040,91 @@
       <c r="D48" s="4">
         <v>400</v>
       </c>
-    </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B49" s="4" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="D49" s="4">
         <v>400</v>
       </c>
-    </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B50" s="4" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="D50" s="4">
         <v>400</v>
       </c>
-    </row>
-    <row r="53" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="E50" s="1"/>
+      <c r="F50" s="1"/>
+    </row>
+    <row r="53" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B53" s="17" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="54" spans="2:4" x14ac:dyDescent="0.4">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="54" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B54" s="17" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="55" spans="2:4" x14ac:dyDescent="0.4">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B55" s="15" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D55" s="15" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="56" spans="2:4" x14ac:dyDescent="0.4">
+        <v>222</v>
+      </c>
+      <c r="E55" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="F55" s="21" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B56" s="4" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>94</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="57" spans="2:4" x14ac:dyDescent="0.4">
+        <v>273</v>
+      </c>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+    </row>
+    <row r="57" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B57" s="4" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="58" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+    </row>
+    <row r="58" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B58" s="4" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>74</v>
@@ -5974,131 +6132,174 @@
       <c r="D58" s="4" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="60" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+    </row>
+    <row r="60" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B60" s="17" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="61" spans="2:4" x14ac:dyDescent="0.4">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="61" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B61" s="15" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="62" spans="2:4" x14ac:dyDescent="0.4">
+        <v>222</v>
+      </c>
+      <c r="E61" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="F61" s="21" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="62" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B62" s="4" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="C62" s="4" t="s">
         <v>65</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="63" spans="2:4" x14ac:dyDescent="0.4">
+        <v>277</v>
+      </c>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+    </row>
+    <row r="63" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B63" s="4" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="64" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+    </row>
+    <row r="64" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B64" s="4" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="65" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-    </row>
-    <row r="66" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B66" s="17" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="67" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B67" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="C67" s="15" t="s">
-        <v>227</v>
-      </c>
-      <c r="D67" s="15" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="68" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B68" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="69" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+    </row>
+    <row r="65" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B65" s="4" t="s">
+        <v>342</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+    </row>
+    <row r="66" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+    </row>
+    <row r="67" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B67" s="17" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B68" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="C68" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="D68" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="E68" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="F68" s="21" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="69" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B69" s="4" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="C69" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="E69" s="1"/>
+      <c r="F69" s="1"/>
+    </row>
+    <row r="70" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B70" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C70" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="D69" s="4" t="s">
+      <c r="D70" s="4" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="70" spans="2:4" x14ac:dyDescent="0.4">
-      <c r="B70" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="71" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+    </row>
+    <row r="71" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B71" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="D71" s="4" t="s">
         <v>290</v>
       </c>
-      <c r="C71" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="D71" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="72" spans="2:4" x14ac:dyDescent="0.4">
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
+    </row>
+    <row r="72" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B72" s="4" t="s">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="D72" s="4" t="s">
         <v>83</v>
       </c>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+    </row>
+    <row r="73" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B73" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/設計資料/ペアプログラミング2_チーム2_基本仕様R0.xlsx
+++ b/設計資料/ペアプログラミング2_チーム2_基本仕様R0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s_ochi\Documents\GitHub\WebAPI_Pair_Programming_Team2\設計資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83F840DF-6B9A-4F16-8E16-26B0A811F886}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A3CE9D4-4AD8-4E32-8D91-35D7B5D8C441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{364D4863-AD58-4424-8EC0-C144B033B4FB}"/>
+    <workbookView xWindow="-25245" yWindow="1725" windowWidth="21600" windowHeight="11295" activeTab="7" xr2:uid="{364D4863-AD58-4424-8EC0-C144B033B4FB}"/>
   </bookViews>
   <sheets>
     <sheet name="スケジュール" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="362">
   <si>
     <t>作るもの決定</t>
   </si>
@@ -638,10 +638,6 @@
   </si>
   <si>
     <t xml:space="preserve">    "chatId": 1,</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t xml:space="preserve">    "userId": 1,</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1482,6 +1478,83 @@
   </si>
   <si>
     <t>エビデンス</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>〇</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>目視確認</t>
+    <rPh sb="0" eb="4">
+      <t>モクシカクニン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>F-04</t>
+  </si>
+  <si>
+    <t>ユーザー名未入力</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー名＆パスワード未入力</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パスワード未入力</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>エラーメッセージ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>テキストエリアの入力制限で30文字以下しか入力できない</t>
+    <rPh sb="15" eb="17">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>イカ</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>ニュウリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パスワード7文字</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>パスワード31文字</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー名未入力＆パスワード7文字</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>サーバーエラー</t>
+  </si>
+  <si>
+    <t>サーバーエラー</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>アラート</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>NG</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ログイン失敗</t>
+    <rPh sb="4" eb="6">
+      <t>シッパイ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -1612,7 +1685,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1676,8 +1749,11 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3406,6 +3482,627 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>82690</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1857375</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>1977223</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12BC84D3-31D0-0F55-71FC-1F1D058786FF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6972300" y="17570590"/>
+          <a:ext cx="1724025" cy="1894533"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>76201</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1839103</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>1752601</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F80F4920-D043-B982-1A3F-505C2241DBEA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6972300" y="15668626"/>
+          <a:ext cx="1705753" cy="1676400"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>238126</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1748810</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>1666875</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4ECC5422-5278-29DF-6076-BE6B55E216FC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7077076" y="13506450"/>
+          <a:ext cx="1510684" cy="1495425"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>114301</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1933575</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>2104113</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="図 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79C6672F-3857-F0DC-0EEA-C7143445D1C9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6934200" y="20926426"/>
+          <a:ext cx="1838325" cy="1989812"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>201543</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>314325</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1942179</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>2219909</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3ADFEF03-A1BF-B946-AD02-F9DDAD471372}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7040493" y="27479625"/>
+          <a:ext cx="1740636" cy="1905584"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>193334</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1982808</xdr:colOff>
+      <xdr:row>67</xdr:row>
+      <xdr:rowOff>2048469</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{366B2245-7B87-8D4A-9A8A-9B53607F2F89}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7032284" y="25069800"/>
+          <a:ext cx="1789474" cy="1886544"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1842531</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>2071699</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9ECD8D5E-1B63-4B8F-9D0D-C38856EDDAB9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6981825" y="30994350"/>
+          <a:ext cx="1699656" cy="1938349"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>115190</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>171451</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1880517</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>2000251</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{486CB813-8DC0-0060-159B-913644E54759}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6954140" y="30527626"/>
+          <a:ext cx="1765327" cy="1828800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1995662</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>2152650</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B1B9261C-55A8-34C1-78AE-A28AD93C5EE1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6972300" y="32708850"/>
+          <a:ext cx="1862312" cy="2028825"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2247900</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>619125</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>6934854</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>1447916</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{85BBDDC7-21ED-663B-E8CA-6454D34DFF05}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9086850" y="33204150"/>
+          <a:ext cx="4686954" cy="828791"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>447675</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>213488</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>6907525</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>2410470</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="図 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1633F03A-D26E-DFF2-7405-0CC594DBA4ED}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7286625" y="35027363"/>
+          <a:ext cx="6459850" cy="2196982"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1123950</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>1209675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>6230063</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>1943202</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="図 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07E9B2AC-12C1-B9E1-8BBC-4A2651E88DB9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7962900" y="38300025"/>
+          <a:ext cx="5106113" cy="733527"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>361950</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>4960669</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>1867482</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="18" name="図 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FEB48402-40A4-1731-C712-BCB7A924BB83}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7038975" y="19688175"/>
+          <a:ext cx="4760644" cy="1505532"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2066925</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>952500</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>7030143</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>1562185</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="図 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F34EE496-4004-DA30-D2D6-0F18E96A5688}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8905875" y="20278725"/>
+          <a:ext cx="4963218" cy="609685"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
   <a:themeElements>
@@ -3931,7 +4628,7 @@
   <sheetData>
     <row r="2" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="K2" t="s">
         <v>55</v>
@@ -3942,7 +4639,7 @@
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="K3" t="s">
         <v>113</v>
@@ -3950,12 +4647,12 @@
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B5" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>78</v>
@@ -3963,12 +4660,12 @@
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B7" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K7" t="s">
         <v>75</v>
@@ -3977,12 +4674,12 @@
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B8" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B9" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>77</v>
@@ -3995,23 +4692,23 @@
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B12" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B13" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C13" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C14" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="K14" t="s">
         <v>26</v>
@@ -4020,13 +4717,13 @@
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.4">
       <c r="C15" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="N15" s="2"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.4">
       <c r="C16" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="K16" t="s">
         <v>22</v>
@@ -4037,7 +4734,7 @@
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.4">
       <c r="C17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="N17" s="2"/>
     </row>
@@ -4049,16 +4746,16 @@
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B19" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="N19" s="2"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B20" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C20" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>78</v>
@@ -4066,127 +4763,127 @@
     </row>
     <row r="21" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B21" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C21" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="N21" s="2"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.4">
       <c r="C22" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.4">
       <c r="C23" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.4">
       <c r="C24" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B26" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B27" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C27" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B28" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C28" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.4">
       <c r="C29" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.4">
       <c r="C30" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.4">
       <c r="C31" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B33" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B34" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C34" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B35" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C35" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C36" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C37" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C38" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B40" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B41" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C41" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B42" t="s">
+        <v>139</v>
+      </c>
+      <c r="C42" t="s">
+        <v>318</v>
+      </c>
+      <c r="D42" t="s">
         <v>140</v>
-      </c>
-      <c r="C42" t="s">
-        <v>319</v>
-      </c>
-      <c r="D42" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C43" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D43" t="s">
         <v>70</v>
@@ -4194,48 +4891,48 @@
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C44" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D44" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C45" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D45" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B48" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B49" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B50" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B51" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B52" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B53" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.4">
@@ -4243,12 +4940,12 @@
         <v>70</v>
       </c>
       <c r="C55" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C56" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.4">
@@ -4256,17 +4953,17 @@
         <v>72</v>
       </c>
       <c r="C58" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C59" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B61" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.4">
@@ -4274,22 +4971,22 @@
         <v>56</v>
       </c>
       <c r="C62" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C63" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C64" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C65" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.4">
@@ -4297,17 +4994,17 @@
         <v>54</v>
       </c>
       <c r="C67" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C68" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C69" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -4340,7 +5037,7 @@
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -4525,10 +5222,10 @@
         <v>116</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -4574,13 +5271,13 @@
         <v>96</v>
       </c>
       <c r="I4" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="K4" s="10" t="s">
         <v>96</v>
       </c>
       <c r="L4" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="2:12" x14ac:dyDescent="0.4">
@@ -4629,7 +5326,7 @@
         <v>110</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L6" s="11" t="s">
         <v>123</v>
@@ -4666,13 +5363,13 @@
         <v>100</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>100</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H8" s="11" t="s">
         <v>100</v>
@@ -4684,7 +5381,7 @@
         <v>122</v>
       </c>
       <c r="L8" s="12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" spans="2:12" x14ac:dyDescent="0.4">
@@ -4698,7 +5395,7 @@
         <v>115</v>
       </c>
       <c r="K10" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.4">
@@ -4712,35 +5409,35 @@
         <v>103</v>
       </c>
       <c r="K11" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B12" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>104</v>
       </c>
       <c r="K12" s="13" t="s">
-        <v>125</v>
+        <v>145</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.4">
       <c r="B13" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>124</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.4">
@@ -4751,71 +5448,71 @@
         <v>107</v>
       </c>
       <c r="H14" s="13" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K14" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.4">
       <c r="H15" s="13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.4">
       <c r="H16" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K16" s="13"/>
     </row>
     <row r="17" spans="5:11" x14ac:dyDescent="0.4">
       <c r="E17" s="14"/>
       <c r="H17" s="13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K17" s="13"/>
     </row>
     <row r="18" spans="5:11" x14ac:dyDescent="0.4">
       <c r="E18" s="14"/>
       <c r="H18" s="13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="19" spans="5:11" x14ac:dyDescent="0.4">
       <c r="E19" s="14"/>
       <c r="H19" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K19" s="13"/>
     </row>
     <row r="20" spans="5:11" x14ac:dyDescent="0.4">
       <c r="E20" s="14"/>
       <c r="H20" s="13" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="K20" s="13"/>
     </row>
     <row r="21" spans="5:11" x14ac:dyDescent="0.4">
       <c r="H21" s="13" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="K21" s="13"/>
     </row>
     <row r="22" spans="5:11" x14ac:dyDescent="0.4">
       <c r="H22" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K22" s="13"/>
     </row>
     <row r="23" spans="5:11" x14ac:dyDescent="0.4">
       <c r="H23" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K23" s="13"/>
     </row>
     <row r="24" spans="5:11" x14ac:dyDescent="0.4">
       <c r="H24" s="13" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K24" s="13"/>
     </row>
@@ -4853,33 +5550,33 @@
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B2" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="C2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E2" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="C2" t="s">
-        <v>171</v>
-      </c>
-      <c r="E2" s="17" t="s">
-        <v>198</v>
-      </c>
       <c r="F2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B3" s="17" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E3" s="7"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B5" s="17" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="E5" s="17" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.4">
@@ -4887,13 +5584,13 @@
         <v>90</v>
       </c>
       <c r="C6" s="16" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="E6" s="16" t="s">
         <v>90</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.4">
@@ -4901,13 +5598,13 @@
         <v>91</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E7" s="19" t="s">
         <v>91</v>
       </c>
       <c r="F7" s="19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.4">
@@ -4915,13 +5612,13 @@
         <v>93</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E8" s="19" t="s">
         <v>93</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.4">
@@ -4929,13 +5626,13 @@
         <v>92</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="E9" s="19" t="s">
         <v>92</v>
       </c>
       <c r="F9" s="19" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.4">
@@ -4952,94 +5649,94 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B12" s="7" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E12" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B13" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E13" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B14" s="7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E14" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B15" s="7" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E15" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B16" s="7" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E16" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B17" s="7" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.4">
       <c r="E18" s="17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B19" s="17" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E19" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B20" s="7" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E20" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B21" s="7" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E21" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B22" s="7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E22" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B23" s="7" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B24" s="7" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E24" s="17" t="s">
         <v>72</v>
@@ -5047,87 +5744,87 @@
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B25" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E25" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.4">
       <c r="E26" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B27" s="17" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="E27" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B28" s="7" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E28" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B29" s="7" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E29" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B30" s="7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E30" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.4">
       <c r="B31" s="7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B33" s="17" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="34" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B34" s="7" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="35" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B35" s="7" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="36" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B36" s="7" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="37" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B37" s="7" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="38" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B38" s="7" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="39" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B39" s="7" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -5189,10 +5886,10 @@
     </row>
     <row r="7" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B7" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D7" s="1">
         <v>201</v>
@@ -5210,7 +5907,7 @@
     <row r="9" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D9" s="1">
         <v>400</v>
@@ -5228,7 +5925,7 @@
     <row r="11" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B11" s="1"/>
       <c r="C11" s="1" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D11" s="1">
         <v>400</v>
@@ -5250,7 +5947,7 @@
     </row>
     <row r="14" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B14" s="1" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>66</v>
@@ -5262,7 +5959,7 @@
     <row r="15" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B15" s="1"/>
       <c r="C15" s="1" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D15" s="1">
         <v>400</v>
@@ -5271,7 +5968,7 @@
     <row r="16" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D16" s="1">
         <v>400</v>
@@ -5280,7 +5977,7 @@
     <row r="17" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B17" s="1"/>
       <c r="C17" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D17" s="1">
         <v>400</v>
@@ -5298,7 +5995,7 @@
     <row r="19" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B19" s="1"/>
       <c r="C19" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D19" s="1">
         <v>400</v>
@@ -5307,7 +6004,7 @@
     <row r="20" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D20" s="1">
         <v>409</v>
@@ -5341,7 +6038,7 @@
     <row r="24" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B24" s="1"/>
       <c r="C24" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D24" s="1">
         <v>401</v>
@@ -5359,7 +6056,7 @@
     <row r="26" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B26" s="1"/>
       <c r="C26" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D26" s="1">
         <v>400</v>
@@ -5404,7 +6101,7 @@
         <v>71</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>84</v>
@@ -5413,7 +6110,7 @@
     <row r="33" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B33" s="1"/>
       <c r="C33" s="1" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>84</v>
@@ -5422,7 +6119,7 @@
     <row r="34" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B34" s="1"/>
       <c r="C34" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D34" s="1" t="s">
         <v>84</v>
@@ -5444,10 +6141,10 @@
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B37" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D37" s="1" t="s">
         <v>84</v>
@@ -5456,7 +6153,7 @@
     <row r="38" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B38" s="1"/>
       <c r="C38" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D38" s="1" t="s">
         <v>84</v>
@@ -5465,7 +6162,7 @@
     <row r="39" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B39" s="1"/>
       <c r="C39" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D39" s="1" t="s">
         <v>84</v>
@@ -5474,7 +6171,7 @@
     <row r="40" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B40" s="1"/>
       <c r="C40" s="1" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>84</v>
@@ -5483,7 +6180,7 @@
     <row r="41" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B41" s="1"/>
       <c r="C41" s="1" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>84</v>
@@ -5492,7 +6189,7 @@
     <row r="42" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B42" s="1"/>
       <c r="C42" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>84</v>
@@ -5507,7 +6204,7 @@
         <v>73</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>84</v>
@@ -5516,7 +6213,7 @@
     <row r="45" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B45" s="1"/>
       <c r="C45" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D45" s="1" t="s">
         <v>84</v>
@@ -5539,48 +6236,48 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{74E5BA1B-ABE7-423B-BFCE-8BAA973AD635}">
-  <dimension ref="B2:F73"/>
+  <dimension ref="B2:F82"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="8.875" customWidth="1"/>
     <col min="3" max="3" width="35.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27" customWidth="1"/>
     <col min="6" max="6" width="96" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B2" s="17" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B3" s="17" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B4" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="C4" s="15" t="s">
-        <v>221</v>
-      </c>
       <c r="D4" s="15" t="s">
+        <v>343</v>
+      </c>
+      <c r="E4" s="15" t="s">
         <v>344</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="F4" s="15" t="s">
         <v>345</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B5" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>223</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>224</v>
       </c>
       <c r="D5" s="4">
         <v>201</v>
@@ -5590,10 +6287,10 @@
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B6" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>225</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>226</v>
       </c>
       <c r="D6" s="4">
         <v>201</v>
@@ -5603,10 +6300,10 @@
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B7" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>227</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>228</v>
       </c>
       <c r="D7" s="4">
         <v>201</v>
@@ -5616,10 +6313,10 @@
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B8" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>229</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>230</v>
       </c>
       <c r="D8" s="4">
         <v>201</v>
@@ -5629,32 +6326,32 @@
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B9" s="20" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B10" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="C10" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="D10" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="D10" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="F10" s="15" t="s">
         <v>345</v>
-      </c>
-      <c r="F10" s="21" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B11" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D11" s="4">
         <v>400</v>
@@ -5664,10 +6361,10 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B12" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>235</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>236</v>
       </c>
       <c r="D12" s="4">
         <v>400</v>
@@ -5677,7 +6374,7 @@
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B13" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C13" s="4" t="s">
         <v>74</v>
@@ -5690,10 +6387,10 @@
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B14" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>238</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>239</v>
       </c>
       <c r="D14" s="4">
         <v>400</v>
@@ -5703,10 +6400,10 @@
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B15" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="C15" s="4" t="s">
         <v>240</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>241</v>
       </c>
       <c r="D15" s="4">
         <v>400</v>
@@ -5716,10 +6413,10 @@
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B16" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>340</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>341</v>
       </c>
       <c r="D16" s="4">
         <v>409</v>
@@ -5729,37 +6426,37 @@
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B18" s="17" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B19" s="17" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B20" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="C20" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="D20" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="D20" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="E20" s="21" t="s">
+      <c r="E20" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="F20" s="15" t="s">
         <v>345</v>
-      </c>
-      <c r="F20" s="21" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B21" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="C21" s="4" t="s">
         <v>243</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>244</v>
       </c>
       <c r="D21" s="4">
         <v>200</v>
@@ -5769,45 +6466,45 @@
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B22" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>246</v>
-      </c>
       <c r="D22" s="4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B23" s="20" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B24" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="C24" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="D24" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="D24" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="E24" s="21" t="s">
+      <c r="E24" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="F24" s="15" t="s">
         <v>345</v>
-      </c>
-      <c r="F24" s="21" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B25" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D25" s="4">
         <v>400</v>
@@ -5817,7 +6514,7 @@
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B26" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>74</v>
@@ -5830,10 +6527,10 @@
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B27" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="C27" s="4" t="s">
         <v>249</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>250</v>
       </c>
       <c r="D27" s="4">
         <v>400</v>
@@ -5843,10 +6540,10 @@
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B28" s="4" t="s">
+        <v>250</v>
+      </c>
+      <c r="C28" s="4" t="s">
         <v>251</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>252</v>
       </c>
       <c r="D28" s="4">
         <v>400</v>
@@ -5856,37 +6553,37 @@
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B30" s="17" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B31" s="17" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B32" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="C32" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="D32" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="D32" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="E32" s="21" t="s">
+      <c r="E32" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="F32" s="15" t="s">
         <v>345</v>
-      </c>
-      <c r="F32" s="21" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B33" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>254</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>255</v>
       </c>
       <c r="D33" s="4">
         <v>200</v>
@@ -5896,10 +6593,10 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B34" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C34" s="4" t="s">
         <v>256</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>257</v>
       </c>
       <c r="D34" s="4">
         <v>200</v>
@@ -5909,45 +6606,45 @@
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B35" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>258</v>
       </c>
-      <c r="C35" s="4" t="s">
-        <v>259</v>
-      </c>
       <c r="D35" s="4" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B36" s="20" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B37" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="C37" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="C37" s="15" t="s">
+      <c r="D37" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="D37" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="E37" s="21" t="s">
+      <c r="E37" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="F37" s="15" t="s">
         <v>345</v>
-      </c>
-      <c r="F37" s="21" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B38" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="C38" s="4" t="s">
         <v>260</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>261</v>
       </c>
       <c r="D38" s="4">
         <v>500</v>
@@ -5957,37 +6654,37 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B41" s="17" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B42" s="17" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B43" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="C43" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="C43" s="15" t="s">
+      <c r="D43" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="D43" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="E43" s="21" t="s">
+      <c r="E43" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="F43" s="15" t="s">
         <v>345</v>
-      </c>
-      <c r="F43" s="21" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B44" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D44" s="4">
         <v>201</v>
@@ -5997,10 +6694,10 @@
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B45" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="C45" s="4" t="s">
         <v>264</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>265</v>
       </c>
       <c r="D45" s="4">
         <v>201</v>
@@ -6010,29 +6707,29 @@
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B46" s="20" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B47" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="C47" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="D47" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="D47" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="E47" s="21" t="s">
+      <c r="E47" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="F47" s="15" t="s">
         <v>345</v>
-      </c>
-      <c r="F47" s="21" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B48" s="4" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>63</v>
@@ -6045,10 +6742,10 @@
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B49" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="C49" s="4" t="s">
         <v>267</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>268</v>
       </c>
       <c r="D49" s="4">
         <v>400</v>
@@ -6058,10 +6755,10 @@
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B50" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="C50" s="4" t="s">
         <v>269</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>270</v>
       </c>
       <c r="D50" s="4">
         <v>400</v>
@@ -6071,50 +6768,54 @@
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B53" s="17" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B54" s="17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B55" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="C55" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="C55" s="15" t="s">
+      <c r="D55" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="D55" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="E55" s="21" t="s">
+      <c r="E55" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="F55" s="15" t="s">
         <v>345</v>
-      </c>
-      <c r="F55" s="21" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B56" s="4" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>94</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
+        <v>272</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>347</v>
+      </c>
     </row>
     <row r="57" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B57" s="4" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>150</v>
+        <v>361</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>83</v>
@@ -6122,187 +6823,336 @@
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
     </row>
-    <row r="58" spans="2:6" x14ac:dyDescent="0.4">
+    <row r="58" spans="2:6" ht="143.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B58" s="4" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>74</v>
+        <v>349</v>
       </c>
       <c r="D58" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="F58" s="1"/>
+    </row>
+    <row r="59" spans="2:6" ht="149.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B59" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="D59" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
-    </row>
-    <row r="60" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B60" s="17" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="61" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B61" s="15" t="s">
+      <c r="E59" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="F59" s="1"/>
+    </row>
+    <row r="60" spans="2:6" ht="160.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B60" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E60" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="F60" s="1"/>
+    </row>
+    <row r="61" spans="2:6" ht="160.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B61" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="F61" s="1"/>
+    </row>
+    <row r="62" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B62" s="21"/>
+      <c r="C62" s="21"/>
+      <c r="D62" s="21"/>
+      <c r="E62" s="22"/>
+      <c r="F62" s="22"/>
+    </row>
+    <row r="63" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B63" s="17" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="64" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B64" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="C64" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="C61" s="15" t="s">
+      <c r="D64" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="D61" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="E61" s="21" t="s">
+      <c r="E64" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="F64" s="15" t="s">
         <v>345</v>
       </c>
-      <c r="F61" s="21" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="62" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B62" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
-    </row>
-    <row r="63" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B63" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E63" s="1"/>
-      <c r="F63" s="1"/>
-    </row>
-    <row r="64" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B64" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B65" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="F65" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="66" spans="2:6" ht="170.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B66" s="4"/>
+      <c r="C66" s="4" t="s">
+        <v>349</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="F66" s="1"/>
+    </row>
+    <row r="67" spans="2:6" ht="56.25" x14ac:dyDescent="0.4">
+      <c r="B67" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="F67" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="68" spans="2:6" ht="177.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B68" s="4"/>
+      <c r="C68" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="F68" s="1"/>
+    </row>
+    <row r="69" spans="2:6" ht="195" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B69" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="F69" s="1"/>
+    </row>
+    <row r="70" spans="2:6" ht="37.5" x14ac:dyDescent="0.4">
+      <c r="B70" s="4"/>
+      <c r="C70" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="71" spans="2:6" ht="175.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B71" s="4"/>
+      <c r="C71" s="4" t="s">
+        <v>350</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="F71" s="1"/>
+    </row>
+    <row r="72" spans="2:6" ht="175.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B72" s="4"/>
+      <c r="C72" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="F72" s="1"/>
+    </row>
+    <row r="73" spans="2:6" ht="175.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B73" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="C73" s="4" t="s">
         <v>342</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
-    </row>
-    <row r="66" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B66" s="3"/>
-      <c r="C66" s="3"/>
-      <c r="D66" s="3"/>
-    </row>
-    <row r="67" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B67" s="17" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="68" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B68" s="15" t="s">
-        <v>220</v>
-      </c>
-      <c r="C68" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="D68" s="15" t="s">
-        <v>222</v>
-      </c>
-      <c r="E68" s="21" t="s">
-        <v>345</v>
-      </c>
-      <c r="F68" s="21" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="69" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B69" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="E69" s="1"/>
-      <c r="F69" s="1"/>
-    </row>
-    <row r="70" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B70" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D70" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E70" s="1"/>
-      <c r="F70" s="1"/>
-    </row>
-    <row r="71" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B71" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="D71" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="E71" s="1"/>
-      <c r="F71" s="1"/>
-    </row>
-    <row r="72" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B72" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
-    </row>
-    <row r="73" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B73" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="C73" s="4" t="s">
-        <v>295</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="E73" s="1"/>
+      <c r="E73" s="1" t="s">
+        <v>360</v>
+      </c>
       <c r="F73" s="1"/>
+    </row>
+    <row r="74" spans="2:6" ht="206.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B74" s="4" t="s">
+        <v>341</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+    </row>
+    <row r="75" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B75" s="21"/>
+      <c r="C75" s="21"/>
+      <c r="D75" s="21"/>
+      <c r="E75" s="22"/>
+      <c r="F75" s="22"/>
+    </row>
+    <row r="76" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B76" s="17" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="77" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B77" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="C77" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="D77" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="E77" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="F77" s="15" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="78" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B78" s="4" t="s">
+        <v>279</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+    </row>
+    <row r="79" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B79" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+    </row>
+    <row r="80" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B80" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1"/>
+    </row>
+    <row r="81" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B81" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+    </row>
+    <row r="82" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B82" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/設計資料/ペアプログラミング2_チーム2_基本仕様R0.xlsx
+++ b/設計資料/ペアプログラミング2_チーム2_基本仕様R0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\s_ochi\Documents\GitHub\WebAPI_Pair_Programming_Team2\設計資料\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A3CE9D4-4AD8-4E32-8D91-35D7B5D8C441}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D550464-D60B-4962-91AD-08711ACBC12F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25245" yWindow="1725" windowWidth="21600" windowHeight="11295" activeTab="7" xr2:uid="{364D4863-AD58-4424-8EC0-C144B033B4FB}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7" xr2:uid="{364D4863-AD58-4424-8EC0-C144B033B4FB}"/>
   </bookViews>
   <sheets>
     <sheet name="スケジュール" sheetId="1" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="360">
   <si>
     <t>作るもの決定</t>
   </si>
@@ -1118,15 +1118,6 @@
     <t>L-01</t>
   </si>
   <si>
-    <t>正しいユーザー名・パスワード</t>
-  </si>
-  <si>
-    <t>L-02</t>
-  </si>
-  <si>
-    <t>レスポンスにUserId取得</t>
-  </si>
-  <si>
     <t>L-11</t>
   </si>
   <si>
@@ -1136,15 +1127,9 @@
     <t>L-13</t>
   </si>
   <si>
-    <t>ユーザー名不一致</t>
-  </si>
-  <si>
     <t>L-14</t>
   </si>
   <si>
-    <t>パスワード不一致</t>
-  </si>
-  <si>
     <t>3. チャット一覧 GET /api/chats</t>
   </si>
   <si>
@@ -1169,9 +1154,6 @@
     <t>C-11</t>
   </si>
   <si>
-    <t>DB停止状態</t>
-  </si>
-  <si>
     <t>4. チャット送信 POST /api/chats</t>
   </si>
   <si>
@@ -1239,10 +1221,6 @@
   </si>
   <si>
     <t>F-24</t>
-  </si>
-  <si>
-    <t>UserId返却</t>
-    <phoneticPr fontId="1"/>
   </si>
   <si>
     <t>200 空配列返却</t>
@@ -1547,15 +1525,36 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>NG</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>ログイン失敗</t>
     <rPh sb="4" eb="6">
       <t>シッパイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>正しいユーザー名・パスワード</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ユーザー名/パスワード不一致</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>DB登録失敗</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>U-17</t>
+  </si>
+  <si>
+    <t>DB読出失敗</t>
+    <rPh sb="2" eb="4">
+      <t>ヨミダ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>S-14</t>
   </si>
 </sst>
 </file>
@@ -4100,6 +4099,94 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>171451</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>1838927</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>1819275</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5DC67D7E-67FE-33D9-B3AB-053F8C9B96C6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7010401" y="13496925"/>
+          <a:ext cx="1667476" cy="1657350"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>2257425</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>685800</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>6849116</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>1247853</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="図 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{183DD84B-4128-A41C-EB23-6756E3DCB224}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9096375" y="14020800"/>
+          <a:ext cx="4591691" cy="562053"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -4628,7 +4715,7 @@
   <sheetData>
     <row r="2" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B2" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="K2" t="s">
         <v>55</v>
@@ -4639,7 +4726,7 @@
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="K3" t="s">
         <v>113</v>
@@ -4647,12 +4734,12 @@
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B4" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B5" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="N5" s="2" t="s">
         <v>78</v>
@@ -4660,12 +4747,12 @@
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B6" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B7" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="K7" t="s">
         <v>75</v>
@@ -4674,12 +4761,12 @@
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B8" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B9" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="N9" s="2" t="s">
         <v>77</v>
@@ -4692,15 +4779,15 @@
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B12" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B13" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="C13" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.4">
@@ -4708,7 +4795,7 @@
         <v>139</v>
       </c>
       <c r="C14" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="K14" t="s">
         <v>26</v>
@@ -4717,13 +4804,13 @@
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.4">
       <c r="C15" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="N15" s="2"/>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.4">
       <c r="C16" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="K16" t="s">
         <v>22</v>
@@ -4746,16 +4833,16 @@
     </row>
     <row r="19" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B19" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="N19" s="2"/>
     </row>
     <row r="20" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B20" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="C20" t="s">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>78</v>
@@ -4766,36 +4853,36 @@
         <v>139</v>
       </c>
       <c r="C21" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="N21" s="2"/>
     </row>
     <row r="22" spans="2:14" x14ac:dyDescent="0.4">
       <c r="C22" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.4">
       <c r="C23" t="s">
-        <v>309</v>
+        <v>302</v>
       </c>
     </row>
     <row r="24" spans="2:14" x14ac:dyDescent="0.4">
       <c r="C24" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
     </row>
     <row r="26" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B26" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27" spans="2:14" x14ac:dyDescent="0.4">
       <c r="B27" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="C27" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
     </row>
     <row r="28" spans="2:14" x14ac:dyDescent="0.4">
@@ -4803,35 +4890,35 @@
         <v>139</v>
       </c>
       <c r="C28" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
     </row>
     <row r="29" spans="2:14" x14ac:dyDescent="0.4">
       <c r="C29" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
     </row>
     <row r="30" spans="2:14" x14ac:dyDescent="0.4">
       <c r="C30" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
     </row>
     <row r="31" spans="2:14" x14ac:dyDescent="0.4">
       <c r="C31" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B33" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B34" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="C34" t="s">
-        <v>315</v>
+        <v>308</v>
       </c>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.4">
@@ -4839,12 +4926,12 @@
         <v>139</v>
       </c>
       <c r="C35" t="s">
-        <v>316</v>
+        <v>309</v>
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C36" t="s">
-        <v>307</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.4">
@@ -4854,20 +4941,20 @@
     </row>
     <row r="38" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C38" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
     </row>
     <row r="40" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B40" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
     </row>
     <row r="41" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B41" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="C41" t="s">
-        <v>317</v>
+        <v>310</v>
       </c>
     </row>
     <row r="42" spans="2:4" x14ac:dyDescent="0.4">
@@ -4875,7 +4962,7 @@
         <v>139</v>
       </c>
       <c r="C42" t="s">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="D42" t="s">
         <v>140</v>
@@ -4883,7 +4970,7 @@
     </row>
     <row r="43" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C43" t="s">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="D43" t="s">
         <v>70</v>
@@ -4891,15 +4978,15 @@
     </row>
     <row r="44" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C44" t="s">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="D44" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
     </row>
     <row r="45" spans="2:4" x14ac:dyDescent="0.4">
       <c r="C45" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="D45" t="s">
         <v>142</v>
@@ -4907,7 +4994,7 @@
     </row>
     <row r="48" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B48" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.4">
@@ -4917,22 +5004,22 @@
     </row>
     <row r="50" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B50" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B51" t="s">
-        <v>323</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B52" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B53" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.4">
@@ -4940,12 +5027,12 @@
         <v>70</v>
       </c>
       <c r="C55" t="s">
-        <v>322</v>
+        <v>315</v>
       </c>
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C56" t="s">
-        <v>324</v>
+        <v>317</v>
       </c>
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.4">
@@ -4953,17 +5040,17 @@
         <v>72</v>
       </c>
       <c r="C58" t="s">
-        <v>326</v>
+        <v>319</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C59" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B61" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.4">
@@ -4971,22 +5058,22 @@
         <v>56</v>
       </c>
       <c r="C62" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C63" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="64" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C64" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C65" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.4">
@@ -4994,17 +5081,17 @@
         <v>54</v>
       </c>
       <c r="C67" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C68" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.4">
       <c r="C69" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -5363,7 +5450,7 @@
         <v>100</v>
       </c>
       <c r="C8" s="12" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="E8" s="11" t="s">
         <v>100</v>
@@ -5968,7 +6055,7 @@
     <row r="16" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B16" s="1"/>
       <c r="C16" s="1" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="D16" s="1">
         <v>400</v>
@@ -6004,7 +6091,7 @@
     <row r="20" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B20" s="1"/>
       <c r="C20" s="1" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="D20" s="1">
         <v>409</v>
@@ -6171,7 +6258,7 @@
     <row r="40" spans="2:4" x14ac:dyDescent="0.4">
       <c r="B40" s="1"/>
       <c r="C40" s="1" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>84</v>
@@ -6263,13 +6350,13 @@
         <v>220</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="E4" s="15" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="F4" s="15" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.4">
@@ -6340,10 +6427,10 @@
         <v>221</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="F10" s="15" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.4">
@@ -6413,10 +6500,10 @@
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B16" s="4" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="D16" s="4">
         <v>409</v>
@@ -6424,55 +6511,62 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
     </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B17" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>356</v>
+      </c>
+      <c r="D17" s="4">
+        <v>500</v>
+      </c>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+    </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B18" s="17" t="s">
-        <v>241</v>
-      </c>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B19" s="17" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B20" s="17" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B20" s="15" t="s">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B21" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C21" s="15" t="s">
         <v>220</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D21" s="15" t="s">
         <v>221</v>
       </c>
-      <c r="E20" s="15" t="s">
-        <v>344</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B21" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="D21" s="4">
-        <v>200</v>
-      </c>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
+      <c r="E21" s="15" t="s">
+        <v>337</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>338</v>
+      </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B22" s="4" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>284</v>
+        <v>354</v>
+      </c>
+      <c r="D22" s="4">
+        <v>200</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
@@ -6493,15 +6587,15 @@
         <v>221</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B25" s="4" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>149</v>
@@ -6514,7 +6608,7 @@
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B26" s="4" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>74</v>
@@ -6527,33 +6621,33 @@
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B27" s="4" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>249</v>
+        <v>355</v>
       </c>
       <c r="D27" s="4">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B28" s="4" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>251</v>
+        <v>356</v>
       </c>
       <c r="D28" s="4">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B30" s="17" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.4">
@@ -6572,18 +6666,18 @@
         <v>221</v>
       </c>
       <c r="E32" s="15" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="F32" s="15" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B33" s="4" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="D33" s="4">
         <v>200</v>
@@ -6593,10 +6687,10 @@
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B34" s="4" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="D34" s="4">
         <v>200</v>
@@ -6606,13 +6700,13 @@
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B35" s="4" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
@@ -6633,18 +6727,18 @@
         <v>221</v>
       </c>
       <c r="E37" s="15" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="F37" s="15" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B38" s="4" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>260</v>
+        <v>358</v>
       </c>
       <c r="D38" s="4">
         <v>500</v>
@@ -6654,7 +6748,7 @@
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B41" s="17" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.4">
@@ -6673,18 +6767,18 @@
         <v>221</v>
       </c>
       <c r="E43" s="15" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B44" s="4" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="D44" s="4">
         <v>201</v>
@@ -6694,10 +6788,10 @@
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B45" s="4" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="D45" s="4">
         <v>201</v>
@@ -6721,15 +6815,15 @@
         <v>221</v>
       </c>
       <c r="E47" s="15" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B48" s="4" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>63</v>
@@ -6742,10 +6836,10 @@
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B49" s="4" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="D49" s="4">
         <v>400</v>
@@ -6755,10 +6849,10 @@
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B50" s="4" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D50" s="4">
         <v>400</v>
@@ -6766,14 +6860,27 @@
       <c r="E50" s="1"/>
       <c r="F50" s="1"/>
     </row>
+    <row r="51" spans="2:6" x14ac:dyDescent="0.4">
+      <c r="B51" s="4" t="s">
+        <v>359</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>358</v>
+      </c>
+      <c r="D51" s="4">
+        <v>500</v>
+      </c>
+      <c r="E51" s="1"/>
+      <c r="F51" s="1"/>
+    </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B53" s="17" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
     </row>
     <row r="54" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B54" s="17" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
     </row>
     <row r="55" spans="2:6" x14ac:dyDescent="0.4">
@@ -6787,112 +6894,112 @@
         <v>221</v>
       </c>
       <c r="E55" s="15" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="F55" s="15" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
     </row>
     <row r="56" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B56" s="4" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="C56" s="4" t="s">
         <v>94</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="57" spans="2:6" x14ac:dyDescent="0.4">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6" ht="155.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B57" s="4" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="E57" s="1"/>
+      <c r="E57" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="F57" s="1"/>
     </row>
     <row r="58" spans="2:6" ht="143.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B58" s="4" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="F58" s="1"/>
     </row>
     <row r="59" spans="2:6" ht="149.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B59" s="4" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>83</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="F59" s="1"/>
     </row>
     <row r="60" spans="2:6" ht="160.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B60" s="4" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>83</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="F60" s="1"/>
     </row>
     <row r="61" spans="2:6" ht="160.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B61" s="4" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>83</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="F61" s="1"/>
     </row>
     <row r="62" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B62" s="21"/>
-      <c r="C62" s="21"/>
-      <c r="D62" s="21"/>
-      <c r="E62" s="22"/>
-      <c r="F62" s="22"/>
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+      <c r="D62" s="3"/>
     </row>
     <row r="63" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B63" s="17" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
     </row>
     <row r="64" spans="2:6" x14ac:dyDescent="0.4">
@@ -6906,166 +7013,166 @@
         <v>221</v>
       </c>
       <c r="E64" s="15" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="F64" s="15" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
     </row>
     <row r="65" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B65" s="4" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>65</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="E65" s="1" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
     </row>
     <row r="66" spans="2:6" ht="170.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B66" s="4"/>
       <c r="C66" s="4" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="E66" s="1" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="F66" s="1"/>
     </row>
-    <row r="67" spans="2:6" ht="56.25" x14ac:dyDescent="0.4">
+    <row r="67" spans="2:6" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B67" s="4" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="C67" s="4" t="s">
         <v>235</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="177.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B68" s="4"/>
       <c r="C68" s="4" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="F68" s="1"/>
     </row>
     <row r="69" spans="2:6" ht="195" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B69" s="4" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>83</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="F69" s="1"/>
     </row>
     <row r="70" spans="2:6" ht="37.5" x14ac:dyDescent="0.4">
       <c r="B70" s="4"/>
       <c r="C70" s="4" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="E70" s="1" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
     </row>
     <row r="71" spans="2:6" ht="175.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B71" s="4"/>
       <c r="C71" s="4" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="E71" s="1" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="F71" s="1"/>
     </row>
     <row r="72" spans="2:6" ht="175.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B72" s="4"/>
       <c r="C72" s="4" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="F72" s="1"/>
     </row>
     <row r="73" spans="2:6" ht="175.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B73" s="4" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>83</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>360</v>
+        <v>51</v>
       </c>
       <c r="F73" s="1"/>
     </row>
     <row r="74" spans="2:6" ht="206.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B74" s="4" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="E74" s="1"/>
+        <v>352</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="F74" s="1"/>
     </row>
     <row r="75" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B75" s="21"/>
-      <c r="C75" s="21"/>
-      <c r="D75" s="21"/>
-      <c r="E75" s="22"/>
-      <c r="F75" s="22"/>
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+      <c r="D75" s="3"/>
     </row>
     <row r="76" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B76" s="17" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
     </row>
     <row r="77" spans="2:6" x14ac:dyDescent="0.4">
@@ -7079,28 +7186,28 @@
         <v>221</v>
       </c>
       <c r="E77" s="15" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="F77" s="15" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
     </row>
     <row r="78" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B78" s="4" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="E78" s="1"/>
       <c r="F78" s="1"/>
     </row>
     <row r="79" spans="2:6" ht="18" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B79" s="4" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="C79" s="4" t="s">
         <v>82</v>
@@ -7113,23 +7220,23 @@
     </row>
     <row r="80" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B80" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="D80" s="4" t="s">
         <v>282</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>291</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>289</v>
       </c>
       <c r="E80" s="1"/>
       <c r="F80" s="1"/>
     </row>
     <row r="81" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B81" s="4" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>83</v>
@@ -7139,10 +7246,10 @@
     </row>
     <row r="82" spans="2:6" x14ac:dyDescent="0.4">
       <c r="B82" s="4" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="D82" s="4" t="s">
         <v>83</v>
